--- a/光伏配储项目/电价数据/2026/良村站.xlsx
+++ b/光伏配储项目/电价数据/2026/良村站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.52107</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.00838</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6073500000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.8221499999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6761</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6333300000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42281</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41587</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4443</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.5574199999999999</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19387</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.13494</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.22705</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.48914</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.48521</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.41916</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01917</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.13566</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.21401</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26322</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.12471</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.20013</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.45693</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.55741</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.50343</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.49841</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.68168</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.13168</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.22875</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.24498</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.53747</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.94837</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.71827</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.5997400000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.70159</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.84473</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.74246</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.1338</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.25948</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.96185</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.9307300000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34226</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.73223</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.98268</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.83397</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.00583</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89303</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.92214</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.8920399999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.60864</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42228</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.9085599999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8659600000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9123</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53608</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53686</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49796</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41164</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52654</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.67648</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7241000000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.65091</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.75138</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.59912</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.50162</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.49846</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.75451</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.78862</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.71346</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.81926</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.64358</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.65726</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.02522</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7908500000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.5822200000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.78634</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.48906</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.87236</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.65922</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5967</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6474299999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.63067</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.47793</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.86815</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.64198</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.6360800000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8018500000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.59858</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.05423</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.23287</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.15499</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.0364</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.13431</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.11788</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.28404</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.89067</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.97157</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.29392</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.65351</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.51891</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.53859</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6860700000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33352</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47347</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44422</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.51105</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.5210499999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.45345</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5979800000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.63713</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.89237</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.48025</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7350599999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8813799999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.51069</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5132899999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52303</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.57748</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.65926</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.63536</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.47168</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.64322</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.63447</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.6742100000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.93584</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.45253</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.7705</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.8733200000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.39207</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.68864</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6365299999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.56225</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.74414</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.95828</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9143</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.85421</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.67034</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.84116</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.77013</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.07591</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6904600000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.03041</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6843899999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.70526</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.69133</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.65903</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.75079</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.6617000000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.54475</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.5449700000000001</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.66644</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.44555</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46668</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.5959</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.5885499999999999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.5564600000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.63342</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.50574</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.05653</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.77689</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.5972499999999999</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.74003</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.6242799999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.50286</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.75552</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.46242</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.55992</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.53083</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5285</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.49245</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.5492100000000001</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.5319299999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.03894</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.5408200000000001</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.29511</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.52303</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.51108</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.55403</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.51152</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.56547</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.64118</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.63644</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.67437</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6558099999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.98412</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.62854</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.59872</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.53735</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.5618500000000001</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.58085</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.5837100000000001</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.5546599999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.53559</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.43495</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30273</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.15348</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.15641</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.11496</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.11045</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.12735</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.11247</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.06175</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.16205</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.10836</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.12833</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.13457</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04271</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.09356999999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.09262000000000001</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.08843000000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.10166</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.07124999999999999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.20523</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.11348</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.11237</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11484</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.03526</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.07743000000000001</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.03983</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.15172</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.20582</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48471</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.39024</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.81136</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.55103</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5898600000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.46782</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.46093</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.05191</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.04056</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.02153</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.14509</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.01928</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.03057</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.00108</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03155</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04459</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04449</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04013000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.04192</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.04812</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.24527</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.2127</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33614</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.34707</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.20559</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.19458</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.24561</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.50919</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.48781</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.57467</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46213</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.43389</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.48851</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.54087</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15091</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47958</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.57151</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79328</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.66848</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.45795</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.5684400000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.85012</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.06081</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.5953099999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.06893</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.03481</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.45642</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.49389</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.04354</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.75187</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.37777</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.02699</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.02754</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.47002</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.16107</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.6147699999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8051799999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78886</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8813200000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50649</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41706</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46519</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22416</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5425800000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45784</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59051</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5946</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66226</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.47566</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56463</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.48599</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.03515</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.73168</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.97009</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.9505399999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.9510299999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.51937</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.5037900000000001</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.53579</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.53979</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.41171</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45226</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35323</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47677</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54379</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.43353</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.46823</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.5256799999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.44797</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.4978399999999999</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.45873</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.50299</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.46106</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.47991</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.24591</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.66234</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.5048</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.56516</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.64742</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.43165</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.24396</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.17297</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.96461</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.50261</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.23174</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79535</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.59165</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.46525</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.90079</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.64288</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.64808</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.95938</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.7529400000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.70335</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.49817</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.8396399999999999</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.80921</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.5321399999999999</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.52596</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.50856</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.68343</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.79396</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.58557</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.53706</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.47757</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.55038</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.54208</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.55996</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.70078</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.5615399999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.53126</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.57609</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.51108</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.51763</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.6778</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.5498200000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.5330199999999999</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.5784600000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.5129900000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.50062</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.88662</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.6401699999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.03935</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.78032</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.58741</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.5535399999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.51344</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32472</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.22169</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.21961</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.61509</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.6079600000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.18745</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.19601</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.22261</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.21559</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.21117</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.20234</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20448</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22009</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.20112</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54238</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26507</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26421</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22494</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.46592</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.49704</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.6313099999999999</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.60202</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.50582</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.54731</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.62388</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.62312</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.49559</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.45587</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.48609</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.5754600000000001</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.58069</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.57184</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7898999999999999</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.77911</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.52038</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.6282000000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.91576</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.55511</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.89996</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.7799700000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.7726900000000001</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.84008</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.25936</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.62449</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.9211900000000001</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.59994</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.6083</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.5626599999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.77227</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.75536</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.78874</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.8020900000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.7972100000000001</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.77438</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.79883</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.6466499999999999</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.83199</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.96897</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.90103</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.82889</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.83662</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.8447</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.7900199999999999</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.56288</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.60503</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.82272</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.83108</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.9203300000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.90439</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.22107</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.8545900000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.9593400000000001</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.51949</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.45521</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.59762</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.30133</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.8660599999999999</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.5909500000000001</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3144</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.60739</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.6040099999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.60849</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.53603</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.72611</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.6386900000000001</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.5445099999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.47975</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.83468</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.48823</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65195</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83085</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.24094</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.23855</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.25653</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2145</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.08245999999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.20563</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.12326</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.78518</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.64662</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.66306</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.5568500000000001</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.56212</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.14599</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.55361</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.11868</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.50566</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.45542</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.53721</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.63559</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.15334</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.70508</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.70267</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.17318</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.04806</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.63883</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.7142999999999999</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6716799999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.56836</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.83685</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.72554</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.09902</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41157</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45049</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.86076</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.9728600000000001</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.23585</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.30402</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.46647</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.56934</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.38238</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.24878</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.8654700000000001</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.8737200000000001</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.98621</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.6145900000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.6047400000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.61934</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.07256</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.68069</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.20035</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.76802</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.70777</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.62249</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.7265900000000001</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.52207</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.69198</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.5037699999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.6238400000000001</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.48164</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.57416</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.5892999999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.62091</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.85305</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.8038500000000001</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.70282</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.7039500000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.72265</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.82531</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.10177</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.73512</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.26148</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.15802</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.8735700000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.84566</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78123</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63244</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.18067</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.71158</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.8148200000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.64303</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47166</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.53155</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45811</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.46963</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.45602</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.46784</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.56587</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.81514</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.00352</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.0412</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.45962</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.47287</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.58166</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.25907</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.07252</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.21962</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.11791</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.19687</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19513</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.20635</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.09228</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.06723999999999999</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25107</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25717</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.18821</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.40328</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35169</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.44786</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26696</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17639</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21908</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.44155</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.12317</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.11049</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.06991</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.05702</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.20362</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.06567000000000001</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.06884999999999999</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.05419</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.13377</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.25962</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.08717</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.06886</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.06495999999999999</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.13119</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.06155</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.05519</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.05186</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.06501999999999999</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.15592</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.11211</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.05134</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.05529999999999999</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.05135</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.05342</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.06279</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.05588</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.10644</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.07720999999999999</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19401</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.22266</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.26765</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.49537</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.24458</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.17312</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.60156</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.22007</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26119</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25106</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.24387</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28095</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.19056</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.68106</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.68403</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7962</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.64263</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.57329</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.21999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17791</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.16466</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.34448</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.22189</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.19143</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.02758</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.19394</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.24477</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.11152</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.06606999999999999</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.17975</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.14636</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.24426</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.6993400000000001</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.21979</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.44712</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.6090399999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.54439</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.5465099999999999</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.5478200000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.60952</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.57055</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.46493</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.59423</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.15872</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.80072</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.7891699999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.82699</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.00894</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.8011699999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.84416</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.02891</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.63479</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.56553</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.60729</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7607699999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6547999999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.53835</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.45224</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33082</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.49396</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45811</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.16797</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.94149</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.75175</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6616299999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.6122300000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49427</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.57941</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50437</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.24726</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.6832999999999999</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.59578</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.68623</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.8171</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.81171</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.6069199999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.6246900000000001</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.48147</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.43347</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.17751</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.67716</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.21888</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.40787</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.41347</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.6215499999999999</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.60736</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.8137000000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.53408</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.50883</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6273500000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.57037</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33464</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.56264</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.60405</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.8383700000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.86626</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.09242</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.20257</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.59768</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.5442400000000001</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.51759</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.55138</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.53023</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.6302</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.52218</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.74091</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.5133099999999999</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.53792</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.5390499999999999</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.06197999999999999</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.52089</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.5318999999999999</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.54626</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.54718</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.63797</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.75902</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.78159</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.82857</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.8951399999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.8783</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.9482699999999999</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.96074</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.93851</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.75991</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.66126</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.6403799999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47348</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.7787500000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.59776</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6736799999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.59865</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.57702</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.5502899999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.5604600000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68377</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.51264</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.48487</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.53392</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.50386</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.58801</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.62602</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.59197</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.61215</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.6485599999999999</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6557999999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.56238</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.91369</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.97287</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.58484</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.51239</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.5928300000000001</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.5755800000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.5757000000000001</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.17529</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.19405</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.55263</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.46511</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.4627</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.21989</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.50663</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.58272</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.56643</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.49008</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.73963</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.74193</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.76285</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.42165</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.4352200000000001</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.86818</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.79265</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.67218</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.65286</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.46418</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5376799999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.44103</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.44173</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45561</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5463</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52773</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.20154</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.74999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.58538</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.03894</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.66599</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.53588</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.51475</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.48326</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.5394800000000001</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.46925</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.6337200000000001</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.5628200000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.81977</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.18081</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.82537</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.7387</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.16918</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.03089</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.16844</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.1938</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.04555</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.12168</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.18109</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.58301</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.44908</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.5190499999999999</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.59657</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.52144</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.53401</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.51549</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.04416</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.19802</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.21706</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.26726</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5848099999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5651799999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.57311</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.60492</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.59345</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.57512</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.6989099999999999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.51986</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3753</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06882</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.5969099999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.64535</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.74271</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.46097</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.46261</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.45192</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.7197899999999999</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.48326</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.58077</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.16991</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.07486</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.20107</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.15298</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.8454700000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.44561</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.24191</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.11192</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.88054</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.93429</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.52352</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.1423</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.30517</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.48432</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.0604</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.88802</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.64758</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.58226</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.12305</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.13086</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.6131799999999999</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.13365</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.62697</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.65967</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.6516799999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.64873</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.13528</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.80668</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.83689</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.02152</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.6282300000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.58497</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.6495700000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.91379</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.02504</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.6695399999999999</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.47657</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.42275</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7414400000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.48504</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.48769</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.20737</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.25928</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.5363600000000001</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.23652</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.2182</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.19563</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.20974</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.20351</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.24672</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.16652</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.57056</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.44478</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.47772</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.44169</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.5118199999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.44885</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.48186</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.55537</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.49228</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.47926</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.56932</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5787599999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.55177</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.47215</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46664</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.43535</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
